--- a/output/pdf_financials_xlsx/AUUA.xlsx
+++ b/output/pdf_financials_xlsx/AUUA.xlsx
@@ -1503,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.275313</v>
+        <v>0.261055</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.260483</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7439170000000001</v>
+        <v>0.07110900000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.53685</v>
+        <v>0.504505</v>
       </c>
     </row>
     <row r="49">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12801,10 +12801,10 @@
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>0.032893</v>
+        <v>-0.032893</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>0.249672</v>
+        <v>-0.249672</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AUUA.xlsx
+++ b/output/pdf_financials_xlsx/AUUA.xlsx
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.494825</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.295377</v>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.494825</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.295377</v>
@@ -1503,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.261055</v>
+        <v>1.275313</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.260483</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07110900000000001</v>
+        <v>0.7439170000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.504505</v>
+        <v>0.53685</v>
       </c>
     </row>
     <row r="49">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUUA.xlsx
+++ b/output/pdf_financials_xlsx/AUUA.xlsx
@@ -1077,13 +1077,13 @@
         <v>0.000439</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.264081</v>
+        <v>0.442513</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.266016</v>
+        <v>0.438388</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.265857</v>
+        <v>0.41457</v>
       </c>
     </row>
     <row r="29">
@@ -1099,13 +1099,13 @@
         <v>-0.481131</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.891346</v>
+        <v>-4.712914</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.670179</v>
+        <v>-3.497807</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.344834</v>
+        <v>-1.196121</v>
       </c>
     </row>
     <row r="30">
@@ -1123,13 +1123,13 @@
         <v>-17.53724556503216</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-117.5327980054238</v>
+        <v>-113.2453049076744</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-57.71421346833083</v>
+        <v>-55.00363330208741</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-17.08111584826591</v>
+        <v>-15.19227010139815</v>
       </c>
     </row>
     <row r="31">
@@ -2682,16 +2682,16 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000439</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.442513</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.438388</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.41457</v>
       </c>
     </row>
     <row r="101">
@@ -2949,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.003087</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.027365</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -6301,7 +6301,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6381,7 +6385,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6543,7 +6547,11 @@
           <t>Loss on disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -7101,7 +7109,11 @@
           <t>Proceeds from sale of property and equipment 6</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7958,7 +7970,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -8038,7 +8054,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8200,7 +8216,11 @@
           <t>Loss on disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -8684,7 +8704,11 @@
           <t>Proceeds from sale of property and equipment 7</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -11546,7 +11570,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -11563,10 +11591,10 @@
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>-0.172372</v>
+        <v>0.172372</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>-0.148713</v>
+        <v>0.148713</v>
       </c>
     </row>
     <row r="198">
@@ -11587,7 +11615,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11606,10 +11634,10 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-0.266016</v>
+        <v>0.266016</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-0.265857</v>
+        <v>0.265857</v>
       </c>
     </row>
     <row r="199">
@@ -12178,7 +12206,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -12190,10 +12222,10 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>-0.178432</v>
+        <v>0.178432</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>-0.172372</v>
+        <v>0.172372</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -12219,7 +12251,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12228,13 +12260,13 @@
         </is>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.000439</v>
+        <v>0.000439</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>-0.264081</v>
+        <v>0.264081</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>-0.266016</v>
+        <v>0.266016</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AUUA.xlsx
+++ b/output/pdf_financials_xlsx/AUUA.xlsx
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.745498</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.270254</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.132177</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.132178</v>
       </c>
     </row>
     <row r="71">
@@ -2035,16 +2035,16 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.292284</v>
+        <v>1.037782</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.190662</v>
+        <v>0.460916</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.114522</v>
+        <v>0.246699</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.11946</v>
+        <v>0.251638</v>
       </c>
     </row>
     <row r="72">
@@ -2123,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>5.356406</v>
+        <v>4.610908</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.233081</v>
+        <v>0.962827</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.768865</v>
+        <v>1.636688</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.874682</v>
+        <v>1.742504</v>
       </c>
     </row>
     <row r="76">
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.2398422615850932</v>
+        <v>0.3818155952840731</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.06892837252928705</v>
+        <v>0.0916914270004491</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.06909881760866392</v>
+        <v>0.08550565178490746</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.04195353460519254</v>
+        <v>0.05449519845694779</v>
       </c>
     </row>
     <row r="81">
@@ -2757,7 +2757,7 @@
         <v>0.152346</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.433396</v>
       </c>
     </row>
     <row r="104">
@@ -2823,7 +2823,7 @@
         <v>0.827335</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-1.295611</v>
+        <v>-1.729007</v>
       </c>
     </row>
     <row r="107">
@@ -3018,10 +3018,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="116">
@@ -3034,16 +3034,16 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.025075</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.033355</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.020798</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.017748</v>
       </c>
     </row>
     <row r="117">
@@ -4178,7 +4178,11 @@
           <t>Current portion of lease obligations 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4420,7 +4424,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -5039,7 +5047,11 @@
           <t>Current portion of lease obligations 12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -5207,7 +5219,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -5588,7 +5604,11 @@
           <t>Current portion of lease obligations 13</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -5756,7 +5776,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6793,7 +6817,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7154,7 +7182,11 @@
           <t>Proceeds from sale of investments 8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -7193,7 +7225,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -8749,7 +8785,11 @@
           <t>Proceeds from sale of investments 9</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -8790,7 +8830,11 @@
           <t>Acquisition of intangible assets 8</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
